--- a/cases/boulderfield/published/Boulderfield - Data.xlsx
+++ b/cases/boulderfield/published/Boulderfield - Data.xlsx
@@ -641,7 +641,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>~12,760 ft [S4]</t>
+          <t>~12,760 ft [MA-BF]</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
